--- a/practice/answers/s1_q06.xlsx
+++ b/practice/answers/s1_q06.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,45 +28,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -75,12 +40,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,32 +76,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,222 +462,245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bin fill rates — averaging percentages</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Each bin's fill rate is filled bushels over capacity. The farm's overall rate comes from the two totals, not from averaging the five percentages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
           <t>Bin</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Capacity (bu)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Filled (bu)</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Fill %</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>The formula in D</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Bin 1</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B2" s="3" t="n">
         <v>4200</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C2" s="3" t="n">
         <v>3780</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D2" s="4">
+        <f>C2/B2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bin 2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2800</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D3" s="4">
+        <f>C3/B3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bin 3</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>5225</v>
+      </c>
+      <c r="D4" s="4">
+        <f>C4/B4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bin 4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>3100</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1860</v>
+      </c>
+      <c r="D5" s="4">
         <f>C5/B5</f>
         <v/>
       </c>
-      <c r="E5" s="8">
-        <f>_xlfn.FORMULATEXT(D5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Bin 2</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>2800</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>2100</v>
-      </c>
-      <c r="D6" s="7">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bin 5</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>4600</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>4370</v>
+      </c>
+      <c r="D6" s="4">
         <f>C6/B6</f>
         <v/>
       </c>
-      <c r="E6" s="8">
-        <f>_xlfn.FORMULATEXT(D6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
+    </row>
+    <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Bin 3</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>5500</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>5225</v>
-      </c>
-      <c r="D7" s="7">
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B7" s="6">
+        <f>SUM(B2:B6)</f>
+        <v/>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C2:C6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Overall fill rate</t>
+        </is>
+      </c>
+      <c r="B8" s="8">
         <f>C7/B7</f>
         <v/>
       </c>
-      <c r="E7" s="8">
-        <f>_xlfn.FORMULATEXT(D7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Bin 4</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>3100</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>1860</v>
-      </c>
-      <c r="D8" s="7">
-        <f>C8/B8</f>
-        <v/>
-      </c>
-      <c r="E8" s="8">
-        <f>_xlfn.FORMULATEXT(D8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Bin 5</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>4600</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>4370</v>
-      </c>
-      <c r="D9" s="7">
-        <f>C9/B9</f>
-        <v/>
-      </c>
-      <c r="E9" s="8">
-        <f>_xlfn.FORMULATEXT(D9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="10">
-        <f>SUM(B5:B9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="10">
-        <f>SUM(C5:C9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1"/>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Overall fill rate (totals)</t>
-        </is>
-      </c>
-      <c r="C12" s="11">
-        <f>C10/B10</f>
-        <v/>
-      </c>
-      <c r="E12" s="8">
-        <f>_xlfn.FORMULATEXT(C12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>AVERAGE of the Fill % column</t>
-        </is>
-      </c>
-      <c r="C13" s="11">
-        <f>AVERAGE(D5:D9)</f>
-        <v/>
-      </c>
-      <c r="E13" s="8">
-        <f>_xlfn.FORMULATEXT(C13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1"/>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>85.8% against 83.0%. The overall rate counts every bushel of capacity once. The average of the column counts every bin once, so the 2,800-bushel bin carries the same weight as the 5,500-bushel one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>AVERAGE of Fill %</t>
+        </is>
+      </c>
+      <c r="B9" s="10">
+        <f>AVERAGE(D2:D6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>The 85.8% answers it, because it counts every bushel of capacity once. The 83.0% averages the five bins, treating the 2,800-bushel Bin 2 as equal in weight to the 5,500-bushel Bin 3.</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="n"/>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Averaging a column of percentages goes wrong whenever the things behind them are different sizes -- use the totals, not the average of the ratios.</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n"/>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="14" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A13:G14"/>
+    <mergeCell ref="A11:G12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q06.xlsx
+++ b/practice/answers/s1_q06.xlsx
@@ -1,66 +1,146 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_884D7FDFD678FC5FE36BA09757143EBCB430ED03" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A409A89E-446F-4C3A-B75C-5726BBE22BE7}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Answer" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>Bin</t>
+  </si>
+  <si>
+    <t>Capacity (bu)</t>
+  </si>
+  <si>
+    <t>Filled (bu)</t>
+  </si>
+  <si>
+    <t>Fill %</t>
+  </si>
+  <si>
+    <t>Bin 1</t>
+  </si>
+  <si>
+    <t>Bin 2</t>
+  </si>
+  <si>
+    <t>Bin 3</t>
+  </si>
+  <si>
+    <t>Bin 4</t>
+  </si>
+  <si>
+    <t>Bin 5</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Overall fill rate</t>
+  </si>
+  <si>
+    <t>AVERAGE of Fill %</t>
+  </si>
+  <si>
+    <t>The 85.8% answers it, because it counts every bushel of capacity once. The 83.0% averages the five bins, treating the 2,800-bushel Bin 2 as equal in weight to the 5,500-bushel Bin 3.</t>
+  </si>
+  <si>
+    <t>Averaging a column of percentages goes wrong whenever the things behind them are different sizes -- use the totals, not the average of the ratios.</t>
+  </si>
+  <si>
+    <t>Part (a)</t>
+  </si>
+  <si>
+    <t>Part (b)</t>
+  </si>
+  <si>
+    <t>Part (c)</t>
+  </si>
+  <si>
+    <t>Part (d)</t>
+  </si>
+  <si>
+    <t>Part (e)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
+        <fgColor rgb="FFD9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,100 +156,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -457,244 +480,200 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bin</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (bu)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Filled (bu)</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Fill %</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bin 1</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3">
         <v>4200</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="3">
         <v>3780</v>
       </c>
       <c r="D2" s="4">
         <f>C2/B2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Bin 2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3">
         <v>2800</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="3">
         <v>2100</v>
       </c>
       <c r="D3" s="4">
         <f>C3/B3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Bin 3</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3">
         <v>5500</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="3">
         <v>5225</v>
       </c>
       <c r="D4" s="4">
         <f>C4/B4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Bin 4</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3">
         <v>3100</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="3">
         <v>1860</v>
       </c>
       <c r="D5" s="4">
         <f>C5/B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Bin 5</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3">
         <v>4600</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="3">
         <v>4370</v>
       </c>
       <c r="D6" s="4">
         <f>C6/B6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="B7" s="6">
         <f>SUM(B2:B6)</f>
-        <v/>
+        <v>20200</v>
       </c>
       <c r="C7" s="6">
         <f>SUM(C2:C6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Overall fill rate</t>
-        </is>
+        <v>17335</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="7" t="s">
+        <v>10</v>
       </c>
       <c r="B8" s="8">
         <f>C7/B7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>AVERAGE of Fill %</t>
-        </is>
+        <v>0.85816831683168315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="B9" s="10">
         <f>AVERAGE(D2:D6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>The 85.8% answers it, because it counts every bushel of capacity once. The 83.0% averages the five bins, treating the 2,800-bushel Bin 2 as equal in weight to the 5,500-bushel Bin 3.</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Averaging a column of percentages goes wrong whenever the things behind them are different sizes -- use the totals, not the average of the ratios.</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="14" t="n"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="n"/>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Part (a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Part (b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Part (c)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Part (d)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>Part (e)</t>
-        </is>
+        <v>0.82999999999999985</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="12" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
